--- a/docs/dorpg/DORPG_防具表_v1.xlsx
+++ b/docs/dorpg/DORPG_防具表_v1.xlsx
@@ -4495,14 +4495,14 @@
         <v>40</v>
       </c>
       <c r="H96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M96" t="n">
         <v>2</v>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>重騎士專用頭盔，Lv.40以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+3、INT+2。</t>
+          <t>重騎士專用頭盔，Lv.40以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+4、INT+2。</t>
         </is>
       </c>
     </row>
@@ -4539,14 +4539,14 @@
         <v>50</v>
       </c>
       <c r="H97" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M97" t="n">
         <v>3</v>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>重騎士專用頭盔，Lv.50以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+4、INT+3。</t>
+          <t>重騎士專用頭盔，Lv.50以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+6、INT+3。</t>
         </is>
       </c>
     </row>
@@ -4583,14 +4583,14 @@
         <v>60</v>
       </c>
       <c r="H98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M98" t="n">
         <v>3</v>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>重騎士專用頭盔，Lv.60以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+5、INT+3。</t>
+          <t>重騎士專用頭盔，Lv.60以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+6、INT+3。</t>
         </is>
       </c>
     </row>
@@ -4627,14 +4627,14 @@
         <v>70</v>
       </c>
       <c r="H99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M99" t="n">
         <v>4</v>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>重騎士專用頭盔，Lv.70以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+6、INT+4。</t>
+          <t>重騎士專用頭盔，Lv.70以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+7、INT+4。</t>
         </is>
       </c>
     </row>
@@ -4671,14 +4671,14 @@
         <v>80</v>
       </c>
       <c r="H100" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M100" t="n">
         <v>4</v>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>重騎士專用頭盔，Lv.80以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+6、INT+4。</t>
+          <t>重騎士專用頭盔，Lv.80以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+8、INT+4。</t>
         </is>
       </c>
     </row>
@@ -4715,14 +4715,14 @@
         <v>90</v>
       </c>
       <c r="H101" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M101" t="n">
         <v>5</v>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>重騎士專用頭盔，Lv.90以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+7、INT+5。</t>
+          <t>重騎士專用頭盔，Lv.90以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+9、INT+5。</t>
         </is>
       </c>
     </row>
@@ -4847,14 +4847,14 @@
         <v>20</v>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I104" t="n">
         <v>4</v>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>重騎士專用手套，Lv.20以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+1、STR+4。</t>
+          <t>重騎士專用手套，Lv.20以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+2、STR+4。</t>
         </is>
       </c>
     </row>
@@ -4891,14 +4891,14 @@
         <v>30</v>
       </c>
       <c r="H105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I105" t="n">
         <v>5</v>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>重騎士專用手套，Lv.30以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+2、STR+5。</t>
+          <t>重騎士專用手套，Lv.30以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+3、STR+5。</t>
         </is>
       </c>
     </row>
@@ -4935,14 +4935,14 @@
         <v>40</v>
       </c>
       <c r="H106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I106" t="n">
         <v>6</v>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>重騎士專用手套，Lv.40以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+3、STR+6。</t>
+          <t>重騎士專用手套，Lv.40以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+4、STR+6。</t>
         </is>
       </c>
     </row>
@@ -4979,14 +4979,14 @@
         <v>50</v>
       </c>
       <c r="H107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I107" t="n">
         <v>7</v>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>重騎士專用手套，Lv.50以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+4、STR+7。</t>
+          <t>重騎士專用手套，Lv.50以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+5、STR+7。</t>
         </is>
       </c>
     </row>
@@ -5023,14 +5023,14 @@
         <v>60</v>
       </c>
       <c r="H108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I108" t="n">
         <v>8</v>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>重騎士專用手套，Lv.60以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+4、STR+8。</t>
+          <t>重騎士專用手套，Lv.60以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+5、STR+8。</t>
         </is>
       </c>
     </row>
@@ -5067,14 +5067,14 @@
         <v>70</v>
       </c>
       <c r="H109" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I109" t="n">
         <v>9</v>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>重騎士專用手套，Lv.70以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+5、STR+9。</t>
+          <t>重騎士專用手套，Lv.70以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+6、STR+9。</t>
         </is>
       </c>
     </row>
@@ -5111,14 +5111,14 @@
         <v>80</v>
       </c>
       <c r="H110" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I110" t="n">
         <v>10</v>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>重騎士專用手套，Lv.80以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+5、STR+10。</t>
+          <t>重騎士專用手套，Lv.80以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+7、STR+10。</t>
         </is>
       </c>
     </row>
@@ -5155,14 +5155,14 @@
         <v>90</v>
       </c>
       <c r="H111" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I111" t="n">
         <v>11</v>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>重騎士專用手套，Lv.90以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+6、STR+11。</t>
+          <t>重騎士專用手套，Lv.90以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+8、STR+11。</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
         <v>10</v>
       </c>
       <c r="H113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K113" t="n">
         <v>2</v>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.10以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+2、VIT+2、HP上限+4%。</t>
+          <t>重騎士專用衣服，Lv.10以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+3、VIT+2、HP上限+4%。</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5293,7 @@
         <v>20</v>
       </c>
       <c r="H114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K114" t="n">
         <v>3</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.20以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+4、VIT+3、HP上限+5%。</t>
+          <t>重騎士專用衣服，Lv.20以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+5、VIT+3、HP上限+5%。</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
         <v>30</v>
       </c>
       <c r="H115" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K115" t="n">
         <v>4</v>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.30以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+6、VIT+4、HP上限+7%。</t>
+          <t>重騎士專用衣服，Lv.30以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+8、VIT+4、HP上限+7%。</t>
         </is>
       </c>
     </row>
@@ -5387,7 +5387,7 @@
         <v>40</v>
       </c>
       <c r="H116" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K116" t="n">
         <v>5</v>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.40以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+8、VIT+5、HP上限+8%。</t>
+          <t>重騎士專用衣服，Lv.40以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+10、VIT+5、HP上限+8%。</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
         <v>50</v>
       </c>
       <c r="H117" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K117" t="n">
         <v>6</v>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.50以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+10、VIT+6、HP上限+10%。</t>
+          <t>重騎士專用衣服，Lv.50以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+13、VIT+6、HP上限+10%。</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
         <v>60</v>
       </c>
       <c r="H118" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K118" t="n">
         <v>7</v>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.60以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+11、VIT+7、HP上限+11%。</t>
+          <t>重騎士專用衣服，Lv.60以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+15、VIT+7、HP上限+11%。</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
         <v>70</v>
       </c>
       <c r="H119" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K119" t="n">
         <v>8</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.70以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+13、VIT+8、HP上限+13%。</t>
+          <t>重騎士專用衣服，Lv.70以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+17、VIT+8、HP上限+13%。</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
         <v>80</v>
       </c>
       <c r="H120" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K120" t="n">
         <v>9</v>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.80以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+15、VIT+9、HP上限+14%。</t>
+          <t>重騎士專用衣服，Lv.80以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+19、VIT+9、HP上限+14%。</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
         <v>90</v>
       </c>
       <c r="H121" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K121" t="n">
         <v>10</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.90以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+16、VIT+10、HP上限+16%。</t>
+          <t>重騎士專用衣服，Lv.90以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+21、VIT+10、HP上限+16%。</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
         <v>20</v>
       </c>
       <c r="H124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K124" t="n">
         <v>3</v>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>重騎士專用褲裙，Lv.20以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+3、VIT+3、HP上限+3%。</t>
+          <t>重騎士專用褲裙，Lv.20以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+4、VIT+3、HP上限+3%。</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
         <v>30</v>
       </c>
       <c r="H125" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K125" t="n">
         <v>3</v>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>重騎士專用褲裙，Lv.30以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+4、VIT+3、HP上限+4%。</t>
+          <t>重騎士專用褲裙，Lv.30以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+6、VIT+3、HP上限+4%。</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
         <v>40</v>
       </c>
       <c r="H126" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K126" t="n">
         <v>4</v>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>重騎士專用褲裙，Lv.40以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+6、VIT+4、HP上限+5%。</t>
+          <t>重騎士專用褲裙，Lv.40以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+7、VIT+4、HP上限+5%。</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
         <v>50</v>
       </c>
       <c r="H127" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K127" t="n">
         <v>5</v>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>重騎士專用褲裙，Lv.50以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+7、VIT+5、HP上限+6%。</t>
+          <t>重騎士專用褲裙，Lv.50以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+9、VIT+5、HP上限+6%。</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
         <v>60</v>
       </c>
       <c r="H128" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K128" t="n">
         <v>6</v>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>重騎士專用褲裙，Lv.60以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+8、VIT+6、HP上限+7%。</t>
+          <t>重騎士專用褲裙，Lv.60以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+11、VIT+6、HP上限+7%。</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>70</v>
       </c>
       <c r="H129" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K129" t="n">
         <v>6</v>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>重騎士專用褲裙，Lv.70以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+9、VIT+6、HP上限+8%。</t>
+          <t>重騎士專用褲裙，Lv.70以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+12、VIT+6、HP上限+8%。</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
         <v>80</v>
       </c>
       <c r="H130" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K130" t="n">
         <v>7</v>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>重騎士專用褲裙，Lv.80以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+10、VIT+7、HP上限+9%。</t>
+          <t>重騎士專用褲裙，Lv.80以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+14、VIT+7、HP上限+9%。</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
         <v>90</v>
       </c>
       <c r="H131" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K131" t="n">
         <v>8</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>重騎士專用褲裙，Lv.90以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+12、VIT+8、HP上限+10%。</t>
+          <t>重騎士專用褲裙，Lv.90以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+15、VIT+8、HP上限+10%。</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
         <v>20</v>
       </c>
       <c r="H134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>2</v>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>重騎士專用鞋子，Lv.20以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+1、AGI+2、DEX+2。</t>
+          <t>重騎士專用鞋子，Lv.20以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+2、AGI+2、DEX+2。</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6280,7 @@
         <v>30</v>
       </c>
       <c r="H135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J135" t="n">
         <v>2</v>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>重騎士專用鞋子，Lv.30以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+2、AGI+2、DEX+2。</t>
+          <t>重騎士專用鞋子，Lv.30以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+3、AGI+2、DEX+2。</t>
         </is>
       </c>
     </row>
@@ -6327,7 +6327,7 @@
         <v>40</v>
       </c>
       <c r="H136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J136" t="n">
         <v>2</v>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>重騎士專用鞋子，Lv.40以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+3、AGI+2、DEX+2。</t>
+          <t>重騎士專用鞋子，Lv.40以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+4、AGI+2、DEX+2。</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6374,7 @@
         <v>50</v>
       </c>
       <c r="H137" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J137" t="n">
         <v>3</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>重騎士專用鞋子，Lv.50以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+4、AGI+3、DEX+3。</t>
+          <t>重騎士專用鞋子，Lv.50以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+5、AGI+3、DEX+3。</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
         <v>60</v>
       </c>
       <c r="H138" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J138" t="n">
         <v>3</v>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>重騎士專用鞋子，Lv.60以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+4、AGI+3、DEX+3。</t>
+          <t>重騎士專用鞋子，Lv.60以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+5、AGI+3、DEX+3。</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
         <v>70</v>
       </c>
       <c r="H139" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J139" t="n">
         <v>3</v>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>重騎士專用鞋子，Lv.70以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+5、AGI+3、DEX+3。</t>
+          <t>重騎士專用鞋子，Lv.70以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+6、AGI+3、DEX+3。</t>
         </is>
       </c>
     </row>
@@ -6515,7 +6515,7 @@
         <v>80</v>
       </c>
       <c r="H140" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J140" t="n">
         <v>4</v>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>重騎士專用鞋子，Lv.80以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+5、AGI+4、DEX+4。</t>
+          <t>重騎士專用鞋子，Lv.80以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+7、AGI+4、DEX+4。</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
         <v>90</v>
       </c>
       <c r="H141" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J141" t="n">
         <v>4</v>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>重騎士專用鞋子，Lv.90以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+6、AGI+4、DEX+4。</t>
+          <t>重騎士專用鞋子，Lv.90以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+8、AGI+4、DEX+4。</t>
         </is>
       </c>
     </row>
@@ -18415,14 +18415,14 @@
         <v>40</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
         <v>2</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>重騎士專用頭盔，Lv.40以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+3、INT+2。</t>
+          <t>重騎士專用頭盔，Lv.40以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+4、INT+2。</t>
         </is>
       </c>
     </row>
@@ -18459,14 +18459,14 @@
         <v>50</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
         <v>3</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>重騎士專用頭盔，Lv.50以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+4、INT+3。</t>
+          <t>重騎士專用頭盔，Lv.50以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+6、INT+3。</t>
         </is>
       </c>
     </row>
@@ -18503,14 +18503,14 @@
         <v>60</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
         <v>3</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>重騎士專用頭盔，Lv.60以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+5、INT+3。</t>
+          <t>重騎士專用頭盔，Lv.60以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+6、INT+3。</t>
         </is>
       </c>
     </row>
@@ -18547,14 +18547,14 @@
         <v>70</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M9" t="n">
         <v>4</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>重騎士專用頭盔，Lv.70以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+6、INT+4。</t>
+          <t>重騎士專用頭盔，Lv.70以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+7、INT+4。</t>
         </is>
       </c>
     </row>
@@ -18591,14 +18591,14 @@
         <v>80</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M10" t="n">
         <v>4</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>重騎士專用頭盔，Lv.80以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+6、INT+4。</t>
+          <t>重騎士專用頭盔，Lv.80以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+8、INT+4。</t>
         </is>
       </c>
     </row>
@@ -18635,14 +18635,14 @@
         <v>90</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M11" t="n">
         <v>5</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>重騎士專用頭盔，Lv.90以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+7、INT+5。</t>
+          <t>重騎士專用頭盔，Lv.90以上可裝備，頭部裝備，兼顧視野與防護，提供DEF+9、INT+5。</t>
         </is>
       </c>
     </row>
@@ -18767,14 +18767,14 @@
         <v>20</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>重騎士專用手套，Lv.20以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+1、STR+4。</t>
+          <t>重騎士專用手套，Lv.20以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+2、STR+4。</t>
         </is>
       </c>
     </row>
@@ -18811,14 +18811,14 @@
         <v>30</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
         <v>5</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>重騎士專用手套，Lv.30以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+2、STR+5。</t>
+          <t>重騎士專用手套，Lv.30以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+3、STR+5。</t>
         </is>
       </c>
     </row>
@@ -18855,14 +18855,14 @@
         <v>40</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>6</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>重騎士專用手套，Lv.40以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+3、STR+6。</t>
+          <t>重騎士專用手套，Lv.40以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+4、STR+6。</t>
         </is>
       </c>
     </row>
@@ -18899,14 +18899,14 @@
         <v>50</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
         <v>7</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>重騎士專用手套，Lv.50以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+4、STR+7。</t>
+          <t>重騎士專用手套，Lv.50以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+5、STR+7。</t>
         </is>
       </c>
     </row>
@@ -18943,14 +18943,14 @@
         <v>60</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
         <v>8</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>重騎士專用手套，Lv.60以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+4、STR+8。</t>
+          <t>重騎士專用手套，Lv.60以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+5、STR+8。</t>
         </is>
       </c>
     </row>
@@ -18987,14 +18987,14 @@
         <v>70</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
         <v>9</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>重騎士專用手套，Lv.70以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+5、STR+9。</t>
+          <t>重騎士專用手套，Lv.70以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+6、STR+9。</t>
         </is>
       </c>
     </row>
@@ -19031,14 +19031,14 @@
         <v>80</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I20" t="n">
         <v>10</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>重騎士專用手套，Lv.80以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+5、STR+10。</t>
+          <t>重騎士專用手套，Lv.80以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+7、STR+10。</t>
         </is>
       </c>
     </row>
@@ -19075,14 +19075,14 @@
         <v>90</v>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
         <v>11</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>重騎士專用手套，Lv.90以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+6、STR+11。</t>
+          <t>重騎士專用手套，Lv.90以上可裝備，手部裝備，強化出拳與擺臂力道，提供DEF+8、STR+11。</t>
         </is>
       </c>
     </row>
@@ -19166,7 +19166,7 @@
         <v>10</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
         <v>2</v>
@@ -19176,7 +19176,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.10以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+2、VIT+2、HP上限+4%。</t>
+          <t>重騎士專用衣服，Lv.10以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+3、VIT+2、HP上限+4%。</t>
         </is>
       </c>
     </row>
@@ -19213,7 +19213,7 @@
         <v>20</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K24" t="n">
         <v>3</v>
@@ -19223,7 +19223,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.20以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+4、VIT+3、HP上限+5%。</t>
+          <t>重騎士專用衣服，Lv.20以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+5、VIT+3、HP上限+5%。</t>
         </is>
       </c>
     </row>
@@ -19260,7 +19260,7 @@
         <v>30</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
         <v>4</v>
@@ -19270,7 +19270,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.30以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+6、VIT+4、HP上限+7%。</t>
+          <t>重騎士專用衣服，Lv.30以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+8、VIT+4、HP上限+7%。</t>
         </is>
       </c>
     </row>
@@ -19307,7 +19307,7 @@
         <v>40</v>
       </c>
       <c r="H26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
         <v>5</v>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.40以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+8、VIT+5、HP上限+8%。</t>
+          <t>重騎士專用衣服，Lv.40以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+10、VIT+5、HP上限+8%。</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
         <v>50</v>
       </c>
       <c r="H27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
         <v>6</v>
@@ -19364,7 +19364,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.50以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+10、VIT+6、HP上限+10%。</t>
+          <t>重騎士專用衣服，Lv.50以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+13、VIT+6、HP上限+10%。</t>
         </is>
       </c>
     </row>
@@ -19401,7 +19401,7 @@
         <v>60</v>
       </c>
       <c r="H28" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K28" t="n">
         <v>7</v>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.60以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+11、VIT+7、HP上限+11%。</t>
+          <t>重騎士專用衣服，Lv.60以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+15、VIT+7、HP上限+11%。</t>
         </is>
       </c>
     </row>
@@ -19448,7 +19448,7 @@
         <v>70</v>
       </c>
       <c r="H29" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K29" t="n">
         <v>8</v>
@@ -19458,7 +19458,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.70以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+13、VIT+8、HP上限+13%。</t>
+          <t>重騎士專用衣服，Lv.70以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+17、VIT+8、HP上限+13%。</t>
         </is>
       </c>
     </row>
@@ -19495,7 +19495,7 @@
         <v>80</v>
       </c>
       <c r="H30" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K30" t="n">
         <v>9</v>
@@ -19505,7 +19505,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.80以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+15、VIT+9、HP上限+14%。</t>
+          <t>重騎士專用衣服，Lv.80以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+19、VIT+9、HP上限+14%。</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
         <v>90</v>
       </c>
       <c r="H31" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K31" t="n">
         <v>10</v>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>重騎士專用衣服，Lv.90以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+16、VIT+10、HP上限+16%。</t>
+          <t>重騎士專用衣服，Lv.90以上可裝備，軀幹裝備，防具主要防禦來源，提供DEF+21、VIT+10、HP上限+16%。</t>
         </is>
       </c>
     </row>
@@ -19683,7 +19683,7 @@
         <v>20</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K34" t="n">
         <v>3</v>
@@ -19693,7 +19693,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>重騎士專用褲裙，Lv.20以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+3、VIT+3、HP上限+3%。</t>
+          <t>重騎士專用褲裙，Lv.20以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+4、VIT+3、HP上限+3%。</t>
         </is>
       </c>
     </row>
@@ -19730,7 +19730,7 @@
         <v>30</v>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K35" t="n">
         <v>3</v>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>重騎士專用褲裙，Lv.30以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+4、VIT+3、HP上限+4%。</t>
+          <t>重騎士專用褲裙，Lv.30以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+6、VIT+3、HP上限+4%。</t>
         </is>
       </c>
     </row>
@@ -19777,7 +19777,7 @@
         <v>40</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K36" t="n">
         <v>4</v>
@@ -19787,7 +19787,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>重騎士專用褲裙，Lv.40以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+6、VIT+4、HP上限+5%。</t>
+          <t>重騎士專用褲裙，Lv.40以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+7、VIT+4、HP上限+5%。</t>
         </is>
       </c>
     </row>
@@ -19824,7 +19824,7 @@
         <v>50</v>
       </c>
       <c r="H37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
         <v>5</v>
@@ -19834,7 +19834,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>重騎士專用褲裙，Lv.50以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+7、VIT+5、HP上限+6%。</t>
+          <t>重騎士專用褲裙，Lv.50以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+9、VIT+5、HP上限+6%。</t>
         </is>
       </c>
     </row>
@@ -19871,7 +19871,7 @@
         <v>60</v>
       </c>
       <c r="H38" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K38" t="n">
         <v>6</v>
@@ -19881,7 +19881,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>重騎士專用褲裙，Lv.60以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+8、VIT+6、HP上限+7%。</t>
+          <t>重騎士專用褲裙，Lv.60以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+11、VIT+6、HP上限+7%。</t>
         </is>
       </c>
     </row>
@@ -19918,7 +19918,7 @@
         <v>70</v>
       </c>
       <c r="H39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K39" t="n">
         <v>6</v>
@@ -19928,7 +19928,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>重騎士專用褲裙，Lv.70以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+9、VIT+6、HP上限+8%。</t>
+          <t>重騎士專用褲裙，Lv.70以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+12、VIT+6、HP上限+8%。</t>
         </is>
       </c>
     </row>
@@ -19965,7 +19965,7 @@
         <v>80</v>
       </c>
       <c r="H40" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K40" t="n">
         <v>7</v>
@@ -19975,7 +19975,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>重騎士專用褲裙，Lv.80以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+10、VIT+7、HP上限+9%。</t>
+          <t>重騎士專用褲裙，Lv.80以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+14、VIT+7、HP上限+9%。</t>
         </is>
       </c>
     </row>
@@ -20012,7 +20012,7 @@
         <v>90</v>
       </c>
       <c r="H41" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K41" t="n">
         <v>8</v>
@@ -20022,7 +20022,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>重騎士專用褲裙，Lv.90以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+12、VIT+8、HP上限+10%。</t>
+          <t>重騎士專用褲裙，Lv.90以上可裝備，下半身裝備，防具次要防禦來源，提供DEF+15、VIT+8、HP上限+10%。</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20153,7 @@
         <v>20</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>2</v>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>重騎士專用鞋子，Lv.20以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+1、AGI+2、DEX+2。</t>
+          <t>重騎士專用鞋子，Lv.20以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+2、AGI+2、DEX+2。</t>
         </is>
       </c>
     </row>
@@ -20200,7 +20200,7 @@
         <v>30</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
         <v>2</v>
@@ -20210,7 +20210,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>重騎士專用鞋子，Lv.30以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+2、AGI+2、DEX+2。</t>
+          <t>重騎士專用鞋子，Lv.30以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+3、AGI+2、DEX+2。</t>
         </is>
       </c>
     </row>
@@ -20247,7 +20247,7 @@
         <v>40</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
         <v>2</v>
@@ -20257,7 +20257,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>重騎士專用鞋子，Lv.40以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+3、AGI+2、DEX+2。</t>
+          <t>重騎士專用鞋子，Lv.40以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+4、AGI+2、DEX+2。</t>
         </is>
       </c>
     </row>
@@ -20294,7 +20294,7 @@
         <v>50</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J47" t="n">
         <v>3</v>
@@ -20304,7 +20304,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>重騎士專用鞋子，Lv.50以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+4、AGI+3、DEX+3。</t>
+          <t>重騎士專用鞋子，Lv.50以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+5、AGI+3、DEX+3。</t>
         </is>
       </c>
     </row>
@@ -20341,7 +20341,7 @@
         <v>60</v>
       </c>
       <c r="H48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J48" t="n">
         <v>3</v>
@@ -20351,7 +20351,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>重騎士專用鞋子，Lv.60以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+4、AGI+3、DEX+3。</t>
+          <t>重騎士專用鞋子，Lv.60以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+5、AGI+3、DEX+3。</t>
         </is>
       </c>
     </row>
@@ -20388,7 +20388,7 @@
         <v>70</v>
       </c>
       <c r="H49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
         <v>3</v>
@@ -20398,7 +20398,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>重騎士專用鞋子，Lv.70以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+5、AGI+3、DEX+3。</t>
+          <t>重騎士專用鞋子，Lv.70以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+6、AGI+3、DEX+3。</t>
         </is>
       </c>
     </row>
@@ -20435,7 +20435,7 @@
         <v>80</v>
       </c>
       <c r="H50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J50" t="n">
         <v>4</v>
@@ -20445,7 +20445,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>重騎士專用鞋子，Lv.80以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+5、AGI+4、DEX+4。</t>
+          <t>重騎士專用鞋子，Lv.80以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+7、AGI+4、DEX+4。</t>
         </is>
       </c>
     </row>
@@ -20482,7 +20482,7 @@
         <v>90</v>
       </c>
       <c r="H51" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J51" t="n">
         <v>4</v>
@@ -20492,7 +20492,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>重騎士專用鞋子，Lv.90以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+6、AGI+4、DEX+4。</t>
+          <t>重騎士專用鞋子，Lv.90以上可裝備，足部裝備，掌管步伐與落地穩定，提供DEF+8、AGI+4、DEX+4。</t>
         </is>
       </c>
     </row>
@@ -36686,7 +36686,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="D2" t="n">
         <v>1.1</v>
